--- a/garrity/progress.xlsx
+++ b/garrity/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewis\OneDrive - The Ohio State University\Desktop\math\garrity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D30AF17-9C5D-4708-9B9B-F0DF44914C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788811F6-9024-4C6B-B1DF-543D6A39F854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09A90C30-3EC0-4E15-9F4D-3CA6F350D8BA}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{09A90C30-3EC0-4E15-9F4D-3CA6F350D8BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
